--- a/tests/resources/EVA_Submission_test_without_data_acknowledgement_sheet.xlsx
+++ b/tests/resources/EVA_Submission_test_without_data_acknowledgement_sheet.xlsx
@@ -2516,17 +2516,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2540,20 +2531,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2825,8 +2825,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1025" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="65"/>
-      <c r="B1" s="65"/>
+      <c r="A1" s="64"/>
+      <c r="B1" s="64"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -2835,10 +2835,10 @@
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:1025" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="68"/>
+      <c r="B2" s="65"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2847,10 +2847,10 @@
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="66" t="s">
         <v>596</v>
       </c>
-      <c r="B3" s="69"/>
+      <c r="B3" s="66"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -2859,10 +2859,10 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="70"/>
+      <c r="B4" s="67"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2871,10 +2871,10 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="71"/>
+      <c r="B5" s="68"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -3924,8 +3924,8 @@
       <c r="AMK7" s="5"/>
     </row>
     <row r="8" spans="1:1025" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="65"/>
-      <c r="B8" s="65"/>
+      <c r="A8" s="64"/>
+      <c r="B8" s="64"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -4951,10 +4951,10 @@
       <c r="AMK8" s="5"/>
     </row>
     <row r="9" spans="1:1025" ht="19" x14ac:dyDescent="0.25">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="70" t="s">
         <v>594</v>
       </c>
-      <c r="B9" s="66"/>
+      <c r="B9" s="70"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -5980,8 +5980,8 @@
       <c r="AMK9" s="5"/>
     </row>
     <row r="10" spans="1:1025" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="65"/>
-      <c r="B10" s="65"/>
+      <c r="A10" s="64"/>
+      <c r="B10" s="64"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -7007,10 +7007,10 @@
       <c r="AMK10" s="5"/>
     </row>
     <row r="11" spans="1:1025" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="67"/>
+      <c r="B11" s="71"/>
     </row>
     <row r="12" spans="1:1025" ht="20" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
@@ -7062,10 +7062,10 @@
       </c>
     </row>
     <row r="19" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="64"/>
+      <c r="B19" s="69"/>
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19"/>
@@ -8091,31 +8091,26 @@
       <c r="AMK19"/>
     </row>
     <row r="20" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="69" t="s">
         <v>595</v>
       </c>
-      <c r="B20" s="64"/>
+      <c r="B20" s="69"/>
     </row>
     <row r="21" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="64"/>
+      <c r="B21" s="69"/>
     </row>
     <row r="22" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="64"/>
+      <c r="B22" s="69"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="FH+E+fpMjhGYrFDO24KAsZWrlGl9RtVhj++RdCSXcffwuxnKX6BjRRieWD0IFQU1y24Ckxwdwy1u1+ejEQ138w==" saltValue="YdFk25tMFJNUo/9PR6+5VQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="13">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
@@ -8124,6 +8119,11 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11069,10 +11069,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="74" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="76"/>
+      <c r="B1" s="74"/>
       <c r="C1" s="72"/>
       <c r="D1" s="42" t="s">
         <v>215</v>
@@ -11138,16 +11138,16 @@
       <c r="I2" s="75"/>
       <c r="J2" s="75"/>
       <c r="K2" s="75"/>
-      <c r="L2" s="74" t="s">
+      <c r="L2" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74" t="s">
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="76" t="s">
         <v>142</v>
       </c>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
       <c r="R2" s="75" t="s">
         <v>149</v>
       </c>
@@ -11391,16 +11391,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AI2"/>
+    <mergeCell ref="AJ2:AS2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="E1:E3"/>
     <mergeCell ref="F2:K2"/>
     <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:V2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AI2"/>
-    <mergeCell ref="AJ2:AS2"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Metadata and VCF" prompt="These sample names must match those provided in the VCF file(s)" sqref="E1 B4:B1003" xr:uid="{00000000-0002-0000-0700-000000000000}">
